--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b1e85f5cd44a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14f18134cb0d544</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e095228ad1f72</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Enterprise Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,382 +986,382 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35eabfbc7f8f7c93</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f8b7c5658d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a673dbe1c9ae038</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea05348c16e9859</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb0dfd2b2eb706e</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1555c7e3029f309e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89b1ad5ce5398d</t>
+          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0687e02ee3d6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEI Consultants</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fc81f1869fd392</t>
+          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be72eebe1e2aa8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a17a91bbbc39e684</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Business Delivery</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1aa3fb43af703</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Associate, Data Engineering - DISC Project</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Population Services International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4aafe4b310cc6782</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, DataOps, MLOps, CI/CD, Terraform, Kubernetes, AKS, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8514be2799f487ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verona, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Sqoop, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c345e76753c929</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning (ML) Ops Engineer - IS Clinical Research - Full Time 8 Hour Days (Exempt) (Non-Union)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2512,81 +2512,81 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4edf6a8d5be469</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PCA Data Engineer</t>
+          <t>Cloud and DevOps Expert</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DPR Construction</t>
+          <t>Fresenius Medical Care</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,365 +2831,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Cloud Storage, Snowflake, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b664fa702865dcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Concord Music Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Transportation Data Scientist</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Downers Grove, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>State Farm</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Cloud and DevOps Expert</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Fresenius Medical Care</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=75e22059c1c4550f</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASPCA</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1300aab23c7eb337</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0555fe5b48f96bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbfd37a40116609</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate, Data Engineering - DISC Project</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Population Services International</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aafe4b310cc6782</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Senior OAS/ODI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>International Logic Systems, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,69 +2201,69 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Cloud and DevOps Expert</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Fresenius Medical Care</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2805,41 +2805,6 @@
         </is>
       </c>
       <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Cloud and DevOps Expert</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Fresenius Medical Care</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=75e22059c1c4550f</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RSVP Communications, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,29 +1256,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,46 +1287,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Senior Drupal Migration Developer (AWS Focus)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>marvica technologies LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbfd37a40116609</t>
+          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbfd37a40116609</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=201b0e84d443e59a</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17a91bbbc39e684</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a17a91bbbc39e684</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Cloud Software Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Stratagen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>Azure, Cloud Storage, Hadoop, Scala, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=22e861ddd0f6e4bb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior OAS/ODI Developer</t>
+          <t>AWS Technical Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>International Logic Systems, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7044ce9c9e0873f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b74e8628189b9b63</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,112 +2201,112 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Snowflake, ETL, ELT, CI/CD, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud and DevOps Expert</t>
+          <t>Enterprise Integration Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fresenius Medical Care</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,15 +2796,470 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=548d3d3d67edadf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AWS Architect</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Waukegan, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, S3, IAM, RDS, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d933bdd873b035b</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AI Data Architect</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56210093c832adbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Services Intern</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ryder System</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Advisor Solution Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HJ Staffing</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Advisor Solution Architect</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HJ Staffing</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sr. Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AI or ML Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cloud and DevOps Expert</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Fresenius Medical Care</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=75e22059c1c4550f</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,35 +783,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RSVP Communications, Inc</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,94 +1196,94 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>RSVP Communications, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=659c3d156cdd9793</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e87d38719548eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,64 +1326,64 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,38 +1392,38 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Drupal Migration Developer (AWS Focus)</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>marvica technologies LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dd7a13fdba852c</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>EDI Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPS Tech Solutions LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbfd37a40116609</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Enterprise Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ketjen</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=5f044f722a79b7cd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17a91bbbc39e684</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Software Architect</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stratagen</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Hadoop, Scala, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e861ddd0f6e4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS Technical Architect</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74e8628189b9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, ETL, Power BI, Tableau, MicroStrategy</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Technical Analyst- Data and Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Data Modeling, Star Schema, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,532 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Cadre5</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Enterprise Integration Architect</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>HealthPartners</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Bloomington, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=548d3d3d67edadf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>AWS Architect</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Waukegan, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, IAM, RDS, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d933bdd873b035b</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AI Data Architect</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Kafka, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56210093c832adbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Services Intern</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Ryder System</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, ETL, Power BI, Tableau, MS Excel, MicroStrategy, Git</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0947e458821ae815</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Advisor Solution Architect</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>HJ Staffing</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d52b697a7ccfabf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Advisor Solution Architect</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>HJ Staffing</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113f0b0e9c716e6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2384ee83565dcea</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8999c659b74b65bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e854254a4a199e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AI or ML Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, MLOps, MLflow, Docker</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Cloud and DevOps Expert</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Fresenius Medical Care</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, MySQL, Azure DevOps, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75e22059c1c4550f</t>
+          <t>https://www.indeed.com/viewjob?jk=646c967b5423d4bf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Verona, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,417 +986,417 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RSVP Communications, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659c3d156cdd9793</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,732 +1476,732 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with AI</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verona, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f044f722a79b7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,382 +2316,382 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,40 +2701,1755 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Violet Ink</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer - AI Platform Team</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Wellmark Blue Cross and Blue Shield</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Computer Programmer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RSVP Communications, Inc</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Quarterhill</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=659c3d156cdd9793</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MDM Developer - Reltio and Informatica</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Interactive Resources</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Integrations</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Opiniion</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI First Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>WTW</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>M.C. Dean, Inc.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Zayo Group</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2, Java, SQL)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EDI Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JPS Tech Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer with AI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VBEST Software Inc</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cloud Platforms Engineer II</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Amcor</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Oshkosh, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Engineer - .NET Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Backend Engineer, POS &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Presto AB</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations-Engineer II</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oracle DBA @ New York, NY</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Infoville Inc</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Developer (contract)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Software Engineer III- ML</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Engineer (copy)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TrueML</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Enterprise Data, Analytics &amp; AI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ketjen</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f044f722a79b7cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SR SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Dollar General</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Goodlettsville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>M-TECH SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Developer – T-2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Finance BI Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Novo Nordisk, Inc.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Lincare</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ConnectOne Bank</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Englewood Cliffs, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CAI (Computer Aid, Inc.)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Opiniion</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cadre5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Arizona Public Service (APS)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Concord Music Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Transportation Data Scientist</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>HNTB Corporation</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sr. Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>Technical Analyst- Data and Systems</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Ascension</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D115" t="n">
         <v>10.4</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, BigQuery, Scala, Data Modeling, Star Schema, Talend, Git, Python</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=646c967b5423d4bf</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>React JS and Node JS Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Radcube LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc21fd5e8801cab</t>
+          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,77 +2621,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
+          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=659c3d156cdd9793</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,94 +2911,94 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cb01c5ecb1bb21</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Contract .NET Full Stack Remote Developer (C#, SQL Server, REST APIs)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RSVP Communications, Inc</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6c7a9ea6b2e318</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI First Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659c3d156cdd9793</t>
+          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,129 +3016,129 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Test Automation Engineer / SDET - HYBRID</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbfd37a40116609</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EDI Developer</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions LLC</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a55f391f402922a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with AI</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Azure Cosmos DB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,42 +3576,42 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>GCP Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Informatica PowerCenter, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6198a7d2f4698</t>
+          <t>https://www.indeed.com/viewjob?jk=a17a91bbbc39e684</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
         </is>
       </c>
     </row>
@@ -3968,52 +3968,52 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Enterprise Integration Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+          <t>https://www.indeed.com/viewjob?jk=548d3d3d67edadf4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Technical Analyst- Data and Systems</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,15 +4441,120 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sr. Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Technical Analyst- Data and Systems</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ascension</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, Redshift, RDS, BigQuery, Scala, Data Modeling, Star Schema, Talend, Git, Python</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=646c967b5423d4bf</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
+          <t>React JS and Node JS Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warrenton, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d393e51b035c281</t>
+          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb1cf3c611caa16</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
+          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>N2IA Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5765fbf481e4537</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
         </is>
       </c>
     </row>
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, ECS, RDS, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
@@ -2848,52 +2848,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659c3d156cdd9793</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c5d065404f67c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full Stack Engineer with AI (FTE)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Amplified Sourcing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Data Modeling, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Test Automation Engineer / SDET - HYBRID</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbfd37a40116609</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bf10e00fee9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Verona, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,102 +3541,102 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GCP Cloud Infrastructure Architect</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17a91bbbc39e684</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enterprise Data, Analytics &amp; AI</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ketjen</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kinesis, Azure, Databricks, Spark, Scala, Kafka, Snowflake, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f044f722a79b7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, DynamoDB, Power BI, Splunk, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ff2151b8007775</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Web Development</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Communify</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=f3befea356e71854</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Enterprise Integration Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=548d3d3d67edadf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, Scala, Data Modeling, ETL, Azure DevOps, Python</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,77 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99671ff321a95d86</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Technical Analyst- Data and Systems</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Ascension</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Data Modeling, Star Schema, Talend, Git, Python</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=646c967b5423d4bf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N2IA Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5765fbf481e4537</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Java Developer-6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1db9cb7feef62593</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
+          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,112 +2621,112 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,129 +2841,129 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>PythonPySpark Engineer-9</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data &amp; AI Engineer – Equities Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer with AI (FTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amplified Sourcing</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Data Modeling, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
+          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,164 +3086,164 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Senior Full Stack Engineer with AI (FTE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Amplified Sourcing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Data Modeling, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,147 +3251,147 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Cloud Data Engineer – EDW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verona, NY, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,77 +3636,77 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Verona, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,59 +3821,59 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,217 +3951,217 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Developer – T-3</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Finance BI Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,42 +4171,42 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Web Development</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Communify</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3befea356e71854</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,15 +4476,260 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cadre5</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>DDN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Web Development</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Communify</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3befea356e71854</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sr. Data Analytics Developer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>West Lake, LA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
+          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4625214c0a1e7d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Full Stack Engineer (React + Node.js)-8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=0e630bded8c035ce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>React JS and Node JS Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
+          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Developer-6</t>
+          <t>Sr. Qlik Data Engineer-9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db9cb7feef62593</t>
+          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer with AWS-5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
+          <t>https://www.indeed.com/viewjob?jk=648b4216f5b7ddf9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python and PySpark, No SQL Developer-7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Sqoop, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
+          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
+          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Data Engineer with Python-8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Java Developer-6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a78121dcb8c69a9a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Databricks Data Engineer-6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce9069d01c3ec7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,94 +1196,94 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Databricks Developer-9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Java Full Stack Developer-6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
+          <t>https://www.indeed.com/viewjob?jk=63cc1ab1ec409b24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
+          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hadoop Developer-8</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,207 +2771,207 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-9</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer – Equities Technology</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,137 +3121,137 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer with AI (FTE)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amplified Sourcing</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Data Modeling, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,15 +3453,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5073a83f76f9253</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer – EDW</t>
+          <t>PythonPySpark Engineer-9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,42 +3541,42 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
+          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Data &amp; AI Engineer – Equities Technology</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,46 +3597,46 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>Interactive Resources</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Verona, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Full Stack Engineer with AI (FTE)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amplified Sourcing</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Data Modeling, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,102 +3786,102 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Data Platform Engineer-8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d72bf837ca83931</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, Snowflake, DynamoDB, ETL, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,207 +3926,207 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Sr DevOPS Engineer-9</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Test Automation Engineer with Payments-9</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=96f189bd2044e159</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Data Analytics Engineer - Network Data Solutions</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Developer – T-3</t>
+          <t>Software Engineer (L2, Java, SQL)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
+          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Cloud Data Engineer – EDW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,102 +4171,102 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,102 +4276,102 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Selenium Automation tester-8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,67 +4556,67 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Developer (contract)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Web Development</t>
+          <t>Senior Data Cloud Engineer(s)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Communify</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3befea356e71854</t>
+          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,42 +4696,1267 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>Data Software Engineer III- ML</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Snowflake Admin-9</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Data Ops Engineer-9</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Python / Linux-8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SR SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Dollar General</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Goodlettsville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>M-TECH SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Developer – T-3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Developer – T-2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Finance BI Developer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Novo Nordisk, Inc.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Lincare</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FiveTran Administrator / Data Integration Engineer-8</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Lebanon, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Anza Mortgage Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Wilmington, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ConnectOne Bank</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Englewood Cliffs, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CAI (Computer Aid, Inc.)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DDN</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Arizona Public Service (APS)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Concord Music Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Transportation Data Scientist</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HNTB Corporation</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Adobe Cloud Architect-9</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-8</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Snowflake Architect-9</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer(Azure + Python)-8</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Devops Engineer-4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71ab8430a5d7c773</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ML Engineer / AI Operations-6</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c17ed9b8feacfce</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>OIPA Engineer-9</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2301f32b095659e</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Resiliency &amp; Recovery Engineer-4</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75e38047a7246a25</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Data Analyst_EDM-9</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Teradata Developer-6</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eb1d5b682ff7668</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Teradata Developer-8</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>StandardAero</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Dallas, TX, US USA</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D157" t="n">
         <v>10.4</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Security Consultant-8</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f04f5ab57b8bc98</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Architect-7</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MAP International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>West Lake, LA, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>28.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d2cecf0a7dedfc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Architect-7</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
+          <t>https://www.indeed.com/viewjob?jk=27eca6e7e11ed7f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-8</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>West Lake, LA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4625214c0a1e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-8</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e630bded8c035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -631,59 +631,59 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4625214c0a1e7d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=0e630bded8c035ce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-9</t>
+          <t>React JS and Node JS Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,46 +692,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
+          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect–Strong Azure Services-strong Finance exp(GL, AR, AP)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffa724aa3602f6ed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer with AWS-5</t>
+          <t>Sr. Qlik Data Engineer-9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648b4216f5b7ddf9</t>
+          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,49 +846,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-7</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Python and PySpark, No SQL Developer-7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
+          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Data Engineer with Python-8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
+          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer with Python-8</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
+          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Developer-6</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78121dcb8c69a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer-6</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce9069d01c3ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c162f75ae66b790</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer-6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce9069d01c3ec7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2ab88683becc31</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Hillspire Consulting</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5073a83f76f9253</t>
+          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-9</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5073a83f76f9253</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer – Equities Technology</t>
+          <t>PythonPySpark Engineer-9</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; AI Engineer – Equities Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
+          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Interactive Resources</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d4138f1f14d7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-8</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d72bf837ca83931</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer – EDW</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Cloud Data Engineer – EDW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Selenium Automation tester-8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Selenium Automation tester-8</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Production Support Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Oracle DBA @ New York, NY</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Infoville Inc</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
         </is>
       </c>
     </row>
@@ -4528,87 +4528,87 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Senior Data Cloud Engineer(s)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Developer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d551426f3f652f40</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Cloud Engineer(s)</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Snowflake Admin-9</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Data Ops Engineer-9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Snowflake Admin-9</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
+          <t>https://www.indeed.com/viewjob?jk=0d6a0fd8e6847f13</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-9</t>
+          <t>Python / Linux-8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Python / Linux-8</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Developer – T-3</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,24 +4896,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Developer – T-3</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Finance BI Developer</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Star Schema, ETL, ELT, Power BI, Git</t>
+          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0588cb9b774de72</t>
+          <t>https://www.indeed.com/viewjob?jk=3601c87165ee5ec5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdcbdad1eb42813</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer-8</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>FiveTran Administrator / Data Integration Engineer-8</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfc555cffe9b704</t>
+          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Adobe Cloud Architect-9</t>
+          <t>Software Development Specialist Advisor</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9a82983350eae0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-8</t>
+          <t>Adobe Cloud Architect-9</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Snowflake Architect-9</t>
+          <t>Azure Databricks Architect-8</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-8</t>
+          <t>Snowflake Architect-9</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Devops Engineer-4</t>
+          <t>Databricks Data Engineer(Azure + Python)-8</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ab8430a5d7c773</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-6</t>
+          <t>OIPA Engineer-9</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c17ed9b8feacfce</t>
+          <t>https://www.indeed.com/viewjob?jk=f2301f32b095659e</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OIPA Engineer-9</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2301f32b095659e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-4</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e38047a7246a25</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst_EDM-9</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Teradata Developer-8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-9</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Security Consultant-8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5850,111 +5850,6 @@
         </is>
       </c>
       <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb1d5b682ff7668</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Teradata Developer-8</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Security Consultant-8</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f04f5ab57b8bc98</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>West Lake, LA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27eca6e7e11ed7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>West Lake, LA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Data Architect-7</t>
+          <t>Full Stack Engineer (React + Node.js)-8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4625214c0a1e7d</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4625214c0a1e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e630bded8c035ce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-8</t>
+          <t>Data Architect–Strong Azure Services-strong Finance exp(GL, AR, AP)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e630bded8c035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ffa724aa3602f6ed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Sr. Qlik Data Engineer-9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,46 +692,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052182e7113c0089</t>
+          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect–Strong Azure Services-strong Finance exp(GL, AR, AP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffa724aa3602f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-9</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Premier Truck Rental</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,84 +811,84 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=0389efa8a7d81fc8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Python and PySpark, No SQL Developer-7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
+          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-7</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer with Python-8</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
+          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Data Engineer with Python-8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0cfa70c2d5d6ef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c162f75ae66b790</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Databricks Data Engineer-6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c162f75ae66b790</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce9069d01c3ec7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer-6</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce9069d01c3ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform (AWS) Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,69 +1221,69 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Developer-9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-9</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Java Full Stack Developer-6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=63cc1ab1ec409b24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-6</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cc1ab1ec409b24</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
+          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,52 +3181,52 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hadoop Developer-8</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=eaee29df30d9cb02</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Violet Ink</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>AI Architect - IT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,52 +3426,52 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=351a87f9d4d66fed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f66b4b40dbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer – Equities Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
+          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PACCAR</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chillicothe, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7aa9de7ae098db</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>Databricks, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d801b3aadeaeee20</t>
+          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer with AI (FTE)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amplified Sourcing</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Data Modeling, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr DevOPS Engineer-9</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-9</t>
+          <t>Cloud Data Engineer – EDW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,102 +3996,102 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Test Automation Engineer with Payments-9</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f189bd2044e159</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Network Data Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba38c8b2c1db3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (L2, Java, SQL)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5775e15ef7e26bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=796c9c330a8616db</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer – EDW</t>
+          <t>Selenium Automation tester-8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
+          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Production Support Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Selenium Automation tester-8</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
+          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Production Support Analyst</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Machine Learning Operations-Engineer II</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,112 +4371,112 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5782d4f63839513</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Oracle DBA @ New York, NY</t>
+          <t>Senior Data Cloud Engineer(s)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Infoville Inc</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Terraform</t>
+          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c95754fdda590</t>
+          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Cloud Engineer(s)</t>
+          <t>Databricks Devops</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
+          <t>https://www.indeed.com/viewjob?jk=1754a97a52563107</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Admin-9</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Data Ops Engineer-9</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Python / Linux-8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
+          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Snowflake Admin-9</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-9</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Developer – T-3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d6a0fd8e6847f13</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Python / Linux-8</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=3601c87165ee5ec5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Developer – T-3</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,42 +4896,42 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdcbdad1eb42813</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,67 +4941,67 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>FiveTran Administrator / Data Integration Engineer-8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,59 +5011,59 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3601c87165ee5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdcbdad1eb42813</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer-8</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Data Architect with HEDIS, CMS Interoperability (FHIR) - Health Care Payer Domain MUST HAVE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=f8371bf27aea78c5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Specialist Advisor</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9a82983350eae0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Adobe Cloud Architect-9</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Azure Databricks Architect-8</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Snowflake Architect-9</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Development Specialist Advisor</t>
+          <t>Databricks Data Engineer(Azure + Python)-8</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9a82983350eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Adobe Cloud Architect-9</t>
+          <t>OIPA Engineer-9</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
+          <t>https://www.indeed.com/viewjob?jk=f2301f32b095659e</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-8</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Snowflake Architect-9</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,24 +5561,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-8</t>
+          <t>Data Analyst_EDM-9</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OIPA Engineer-9</t>
+          <t>Teradata Developer-8</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2301f32b095659e</t>
+          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Walkme</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,24 +5701,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=675aa75207b1417e</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-9</t>
+          <t>Security Consultant-8</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5745,111 +5745,6 @@
         </is>
       </c>
       <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Teradata Developer-8</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Security Consultant-8</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f04f5ab57b8bc98</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Python and PySpark, No SQL Developer-7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Premier Truck Rental</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0389efa8a7d81fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-7</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Premier Truck Rental</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0389efa8a7d81fc8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0cfa70c2d5d6ef</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Data Engineer with Python-8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
+          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer with Python-8</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
+          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0cfa70c2d5d6ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
@@ -1238,25 +1238,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>React Ul Architect (Day 1 Onsite - Plano, TX)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Epochfolio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, MySQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f22daeae7b4cb18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-9</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Databricks Developer-9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-6</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cc1ab1ec409b24</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Java Full Stack Developer-6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
+          <t>https://www.indeed.com/viewjob?jk=63cc1ab1ec409b24</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,69 +3181,69 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Hadoop Developer-8</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hadoop Developer-8</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
+          <t>https://www.indeed.com/viewjob?jk=eaee29df30d9cb02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaee29df30d9cb02</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Violet Ink</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe60e0b6f79b280</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hillspire Consulting</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
+          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hillspire Consulting</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
+          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>Databricks, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr DevOPS Engineer-9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-9</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer – EDW</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Cloud Data Engineer – EDW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Production Support Analyst</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c9c330a8616db</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Selenium Automation tester-8</t>
+          <t>Machine Learning Engineer, Specialist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
+          <t>https://www.indeed.com/viewjob?jk=74e743e45605a878</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=796c9c330a8616db</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Production Support Analyst</t>
+          <t>Selenium Automation tester-8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
@@ -4388,25 +4388,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Westborough, MA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5782d4f63839513</t>
+          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Cloud Engineer(s)</t>
+          <t>Databricks Devops</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
+          <t>https://www.indeed.com/viewjob?jk=1754a97a52563107</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Cloud Engineer(s)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=f5782d4f63839513</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Databricks Devops</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1754a97a52563107</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Snowflake Admin-9</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-9</t>
+          <t>DevOps Miami</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Scala, ELT, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e39fd655a8ea4a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Python / Linux-8</t>
+          <t>Snowflake Admin-9</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
+          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Python / Linux-8</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Data Ops Engineer-9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Developer – T-3</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Developer – T-3</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Developer – T-2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3601c87165ee5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,29 +4896,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdcbdad1eb42813</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4927,11 +4927,11 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,59 +4941,59 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
+          <t>https://www.indeed.com/viewjob?jk=3601c87165ee5ec5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer-8</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdcbdad1eb42813</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e22a77413868eb</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>FiveTran Administrator / Data Integration Engineer-8</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Architect with HEDIS, CMS Interoperability (FHIR) - Health Care Payer Domain MUST HAVE</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8371bf27aea78c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Development Specialist Advisor</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9a82983350eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Adobe Cloud Architect-9</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,24 +5351,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-8</t>
+          <t>Databricks Data Engineer(Azure + Python)-8</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Snowflake Architect-9</t>
+          <t>Data Architect with HEDIS, CMS Interoperability (FHIR) - Health Care Payer Domain MUST HAVE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
+          <t>https://www.indeed.com/viewjob?jk=f8371bf27aea78c5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-8</t>
+          <t>Software Development Specialist Advisor</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9a82983350eae0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OIPA Engineer-9</t>
+          <t>Adobe Cloud Architect-9</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2301f32b095659e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Databricks Architect-8</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Snowflake Architect-9</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-9</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Teradata Developer-8</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Data Analytics Developer</t>
+          <t>Data Analyst_EDM-9</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Teradata Developer-8</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675aa75207b1417e</t>
+          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Security Consultant-8</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,15 +5736,120 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ENCO Electronic Systems</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c206b2cba4b24dcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=675aa75207b1417e</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Security Consultant-8</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f04f5ab57b8bc98</t>
         </is>

--- a/results/job_matches_2026-04-09.xlsx
+++ b/results/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect–Strong Azure Services-strong Finance exp(GL, AR, AP)</t>
+          <t>Sr. Qlik Data Engineer-9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffa724aa3602f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-9</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18e119f478af116</t>
+          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a791a880bde06e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Python and PySpark, No SQL Developer-7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6452beb2eda05bed</t>
+          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-7</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Premier Truck Rental</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84496461a7f60f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0389efa8a7d81fc8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Premier Truck Rental</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0389efa8a7d81fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0cfa70c2d5d6ef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer with Python-8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0cfa70c2d5d6ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer with Python-8</t>
+          <t>Data Engineer-9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1639518b974eada</t>
+          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856795d6d4c99ad</t>
+          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998f352b65a63d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer-9</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e29cba72e164acc</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software</t>
+          <t>Senior Data Engineer, Revenue Intelligence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f11c5f49ca38408</t>
         </is>
       </c>
     </row>
@@ -1203,60 +1203,60 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform (AWS) Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce768659b9bf72c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>React Ul Architect (Day 1 Onsite - Plano, TX)</t>
+          <t>Senior Databricks Developer-9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Epochfolio</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, MySQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f22daeae7b4cb18</t>
+          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>gstv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-9</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77e853a0350e35a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gstv</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5db58126c54d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer-6</t>
+          <t>Software Engineer 2 (backend)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Kafka, Oracle, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cc1ab1ec409b24</t>
+          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca675bb9218f9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8e57ed940ae58</t>
+          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (backend)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f5cd8b68adde4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc78cb23c62b1fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d16a8c657126d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea824309287757b2</t>
+          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cdcb6653d773116</t>
+          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1d9f0daeb4fc95</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a46187d519196e</t>
+          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e0a4162cd6d75f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ada87ca40cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4241a547b4acbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a7ee1efa021caa</t>
+          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f71e3295cf4b39</t>
+          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38329874e51aca06</t>
+          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a561d5957bf89ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19359ed530bcfff</t>
+          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f2b73560369841</t>
+          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe3e6d75490e107</t>
+          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f12357728e0612</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a611b49782f5d80</t>
+          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c27b0fa1c8ca96</t>
+          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3a18454e7dd3b36</t>
+          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a68e770b2c1eedf</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98517d734b86f6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c0d43cd785205c</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b72c1105348d39</t>
+          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f469b10080ad5ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd5b64baedc552</t>
+          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a6912a0cb56a89</t>
+          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1eb71add8ab0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5187c18440b003c0</t>
+          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daae2acbcccdc0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e473affc19c2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bdda68200ab201</t>
+          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4ce952c42fecf7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b269a33149fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693efdefac3b5e22</t>
+          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c70cf3882f7bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632b50be23d1d8da</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857512c549338e29</t>
+          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43cbbdc03af4c4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbfbb793b930789</t>
+          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a099881ceda7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a48b03772b96d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597756563f76f23a</t>
+          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fff4c5da0741fb4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085f46f8851de98</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620c8744c8da0c15</t>
+          <t>https://www.indeed.com/viewjob?jk=eaee29df30d9cb02</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c04b74e271401fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Hadoop Developer-8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b835d39515b49</t>
+          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
+          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaee29df30d9cb02</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hadoop Developer-8</t>
+          <t>AI Architect - IT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc1d899897016c7</t>
+          <t>https://www.indeed.com/viewjob?jk=351a87f9d4d66fed</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hadoop Developer-8</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Hillspire Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d661e7528237a5</t>
+          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75856bb7b17e3cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=a5073a83f76f9253</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Architect - IT</t>
+          <t>PythonPySpark Engineer-9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, ETL</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351a87f9d4d66fed</t>
+          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hillspire Consulting</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
+          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Level Engineer, Global</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5073a83f76f9253</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-9</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PACCAR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chillicothe, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d363ae915dcafdd</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7aa9de7ae098db</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>VCU Health System</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21222c0e738a17da</t>
+          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Senior Specialty Software Engineer (Req #002089)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3667,11 +3667,11 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>Databricks, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,59 +3681,59 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PACCAR</t>
+          <t>M.C. Dean, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chillicothe, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7aa9de7ae098db</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr DevOPS Engineer-9</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VCU Health System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5115841e7866fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer (Req #002089)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112855c709308c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>EMR, Databricks, HBase, Spark, PySpark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18410d10e98da8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Backend / Cloud Infrastructure Engineer - Washington D.C</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>M.C. Dean, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5de6a0b568cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Data Engineer – EDW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-9</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447dcb783ade7ed4</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b3e63e2475ddaa</t>
+          <t>https://www.indeed.com/viewjob?jk=36d097a5c9b38547</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bcea1105f70c11</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer – EDW</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d535062d941699</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Backend Engineer, POS &amp; Integrations</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Presto AB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Production Support Analyst</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka, dbt, CI/CD, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Production Support Analyst</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
         </is>
       </c>
     </row>
@@ -4213,25 +4213,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Selenium Automation tester-8</t>
+          <t>Databricks Devops</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88524bb46a500871</t>
+          <t>https://www.indeed.com/viewjob?jk=1754a97a52563107</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Cloud Engineer(s)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Backend Engineer, POS &amp; Integrations</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Presto AB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a9d868b607be0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb2064fa7d1ef15</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,67 +4346,67 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
+          <t>https://www.indeed.com/viewjob?jk=f5782d4f63839513</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Machine Learning Operations-Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bf6e8f385aab0c</t>
+          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Site Reliability Engineer_Pipeline</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3403085da0b17678</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Databricks Devops</t>
+          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1754a97a52563107</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Cloud Engineer(s)</t>
+          <t>Data Ops Engineer-9</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
+          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DevOps Miami</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Westborough, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, ELT, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5782d4f63839513</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e39fd655a8ea4a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python / Linux-8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deafc80aa75d1193</t>
+          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Falcon NG-SIEM, FrontTier Expansions (Hybrid, Austin)</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, Scala, Kafka, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef92600498a13be</t>
+          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps Miami</t>
+          <t>Snowflake Admin-9</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, ELT, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e39fd655a8ea4a</t>
+          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Snowflake Admin-9</t>
+          <t>Developer – T-3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95b2f9d74363765</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Python / Linux-8</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Lincare</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,42 +4686,42 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a40f795d1fa3e39</t>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-9</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,137 +4731,137 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66a6ade5b8d8d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e22a77413868eb</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db99ec10316c705</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Hybrid - Atlanta GA</t>
+          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22b75c7e14b024</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Developer – T-3</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeacf9553a70181</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Developer – T-2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,67 +4871,67 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23fbf23aaa4ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>FiveTran Administrator / Data Integration Engineer-8</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lincare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Oracle, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>ML Data Engineer - Mortgage Credit Risk</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Anza Mortgage Insurance Corporation</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,59 +4941,59 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3601c87165ee5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ConnectOne Bank</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdcbdad1eb42813</t>
+          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e22a77413868eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer | MLOps &amp; Scalable Systems</t>
+          <t>Databricks Data Engineer(Azure + Python)-8</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Python</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe6c9fa96038f50</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Concord Music Group, Inc.</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, PostgreSQL, Docker, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f8bd2c2f1aed56</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Hadoop, Spark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddc71e55c5a0427</t>
+          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FiveTran Administrator / Data Integration Engineer-8</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Scala, Snowflake, Oracle, MongoDB, Data Modeling, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763aaa9bbc30eda0</t>
+          <t>https://www.indeed.com/viewjob?jk=6abb2385899cf65f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ML Data Engineer - Mortgage Credit Risk</t>
+          <t>Data Analyst_EDM-9</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Anza Mortgage Insurance Corporation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3914f4c8a393dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Teradata Developer-8</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Data Modeling, dbt, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Data Analytics Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,567 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afd96a6073e3e32</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer III</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52a952c18ec91d5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>DDN</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Databricks Data Engineer(Azure + Python)-8</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b9bc4403e88a3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Data Architect with HEDIS, CMS Interoperability (FHIR) - Health Care Payer Domain MUST HAVE</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>VTekis Consulting LLP</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8371bf27aea78c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Development Specialist Advisor</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9a82983350eae0</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Adobe Cloud Architect-9</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fad32cd28d4528</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect-8</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad0aaa34e7ec6cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Snowflake Architect-9</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61bb85adb8cc0c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Press Ganey</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=411ffa408b7d9ea0</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Data Analyst_EDM-9</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d3bc86f8f33c45</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Teradata Developer-8</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45232946272bb1bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Sr. Data Analytics Developer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>StandardAero</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=905b416491d0053a</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>ENCO Electronic Systems</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c206b2cba4b24dcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Walkme</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=675aa75207b1417e</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Security Consultant-8</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f04f5ab57b8bc98</t>
         </is>
       </c>
     </row>
